--- a/docs/Mapping_casi_uso/matrimoni/Matr_005.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_005.xlsx
@@ -908,7 +908,7 @@
     <t>evento.datiEventoMatrimonio.padreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposo</t>
@@ -935,7 +935,7 @@
     <t>evento.datiEventoMatrimonio.padreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(2,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,2,4,5)</t>
   </si>
   <si>
     <t>Impedimento - Sposa</t>
@@ -956,7 +956,7 @@
     <t>evento.datiEventoMatrimonio.madreSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Madre Sposa</t>
@@ -965,7 +965,7 @@
     <t>evento.datiEventoMatrimonio.madreSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,4,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,4,5)</t>
   </si>
   <si>
     <t>Tutore Sposo</t>
@@ -974,13 +974,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposo</t>
@@ -989,7 +989,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposo</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,3)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposo,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposo,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Tutore Sposa</t>
@@ -998,13 +998,13 @@
     <t>evento.datiEventoMatrimonio.assistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,5)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,5)</t>
   </si>
   <si>
     <t>Curatore Sposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3,4)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3,4)</t>
   </si>
   <si>
     <t>Nomina Legale Sposa</t>
@@ -1013,7 +1013,7 @@
     <t>evento.datiEventoMatrimonio.nominaAssistenteLegaleSposa</t>
   </si>
   <si>
-    <t>(evento.datiEventoMatrimonio.regimePatrimoniale.tipo,=,2 &amp;&amp; evento.datiEventoMatrimonio.difettoEta,in,(1,2)) || evento.datiEventoMatrimonio.regimePatrimoniale.tipo,!=,2 || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(1,2,3)</t>
+    <t>evento.datiEventoMatrimonio.tipoAssistenteSposa,==,null || evento.datiEventoMatrimonio.tipoAssistenteSposa,in,(0,1,2,3)</t>
   </si>
   <si>
     <t>Interprete</t>
@@ -1130,13 +1130,13 @@
     <t>attoNotarile</t>
   </si>
   <si>
-    <t>Assistenza minore Sposo</t>
+    <t>Assistenza Sposo</t>
   </si>
   <si>
     <t>tipoAssistenteSposo</t>
   </si>
   <si>
-    <t>Assistenza minore Sposa</t>
+    <t>Assistenza Sposa</t>
   </si>
   <si>
     <t>tipoAssistenteSposa</t>
@@ -1240,7 +1240,7 @@
     <col min="4" max="4" width="62.65625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="33.79296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="218.19921875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="114.08984375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10793,10 +10793,10 @@
         <v>296</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D416" s="2" t="s">
         <v>297</v>
@@ -11621,10 +11621,10 @@
         <v>305</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D452" s="2" t="s">
         <v>306</v>
@@ -12449,10 +12449,10 @@
         <v>312</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D488" s="2" t="s">
         <v>313</v>
@@ -13093,10 +13093,10 @@
         <v>315</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D516" s="2" t="s">
         <v>316</v>
@@ -13737,10 +13737,10 @@
         <v>318</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D544" s="2" t="s">
         <v>319</v>
@@ -14381,10 +14381,10 @@
         <v>321</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D572" s="2" t="s">
         <v>319</v>
@@ -15186,10 +15186,10 @@
         <v>326</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D607" s="2" t="s">
         <v>327</v>
@@ -15830,10 +15830,10 @@
         <v>329</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D635" s="2" t="s">
         <v>327</v>
@@ -17038,7 +17038,7 @@
         <v>373</v>
       </c>
       <c r="F687" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G687" s="2" t="s">
         <v>55</v>
